--- a/development/evidence/client-demo/emerald-DEMO-duty-2026-10-21-2026-10-21.xlsx
+++ b/development/evidence/client-demo/emerald-DEMO-duty-2026-10-21-2026-10-21.xlsx
@@ -34,7 +34,7 @@
     <t>All sales executives</t>
   </si>
   <si>
-    <t>Sessions: 3 · Duty: 180.71 min · Breaks: 20.33 min · Duty less breaks: 160.38 min</t>
+    <t>Sessions: 3 · Duty: 180.81 min · Breaks: 20.38 min · Duty less breaks: 160.43 min</t>
   </si>
   <si>
     <t>Browser-local sample records. Not actual company activity. UAE time.</t>
@@ -64,19 +64,19 @@
     <t>Ahmed Hassan</t>
   </si>
   <si>
-    <t>21/10/2026, 07:25</t>
+    <t>21/10/2026, 07:37</t>
   </si>
   <si>
     <t>Ended</t>
   </si>
   <si>
-    <t>21/10/2026, 07:25 → 21/10/2026, 07:25</t>
+    <t>21/10/2026, 07:37 → 21/10/2026, 07:37</t>
   </si>
   <si>
     <t>Shihab K.</t>
   </si>
   <si>
-    <t>21/10/2026, 05:55</t>
+    <t>21/10/2026, 06:07</t>
   </si>
   <si>
     <t/>
@@ -85,7 +85,7 @@
     <t>On duty</t>
   </si>
   <si>
-    <t>21/10/2026, 06:00 → 21/10/2026, 06:05</t>
+    <t>21/10/2026, 06:12 → 21/10/2026, 06:17</t>
   </si>
   <si>
     <t>Naseer M.</t>
@@ -94,7 +94,7 @@
     <t>On break</t>
   </si>
   <si>
-    <t>21/10/2026, 07:10 → Ongoing</t>
+    <t>21/10/2026, 07:22 → Ongoing</t>
   </si>
 </sst>
 </file>
@@ -600,13 +600,13 @@
         <v>23</v>
       </c>
       <c r="E10" s="1">
-        <v>90.31</v>
+        <v>90.36</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>85.31</v>
+        <v>85.36</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>24</v>
@@ -626,10 +626,10 @@
         <v>26</v>
       </c>
       <c r="E11" s="1">
-        <v>90.31</v>
+        <v>90.36</v>
       </c>
       <c r="F11" s="1">
-        <v>15.31</v>
+        <v>15.36</v>
       </c>
       <c r="G11" s="1">
         <v>75</v>
